--- a/output/2026-09-20_06_Croazia_Vukovarsko-srijemska_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-20_06_Croazia_Vukovarsko-srijemska_Depolverazione_Trattamento_aria.xlsx
@@ -494,10 +494,9 @@
           <t>0800 200 308</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Grossista/rivenditore generalista di utensili, macchine, elettroutensili e piccoli elettrodomestici (web shop attivo dal 1990). Confermata vendita diretta di aspiratore industriale (EVC15 1200W DENZEL) e ventilatori. Filiale anche a Vukovar oltre alla sede di Vinkovci.</t>
+          <t>Grossista/rivenditore generalista di utensili, macchine, elettroutensili e piccoli elettrodomestici (web shop attivo dal 1990). Confermata vendita diretta di aspiratore industriale (EVC15 1200W DENZEL) e ventilatori. Filiale anche a Vukovar oltre alla sede di Vinkovci. [DUPLICATO — vedi anche: 2026-09-20_05_Croazia_Vukovarsko-srijemska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -532,7 +531,6 @@
           <t>032/354 240 (fisso), 099/8548 382 (mobile)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Rivenditore di utensili professionali/elettroutensili (Makita, DeWalt, Bosch), DPI, abrasivi; gestisce anche 'Hidraulika Flex' (tubi idraulici, gas tecnici). Profilo generalista di attrezzature tecniche; nessun collegamento esplicito a depolverazione.</t>
@@ -565,8 +563,6 @@
           <t>Depolverazione / Trattamento aria</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Installatore/manutentore di impianti a gas, idrici, riscaldamento, ventilazione e climatizzazione a Vukovar.</t>
